--- a/luban-excels/bak/xlsx/__enums__ - 副本.xlsx
+++ b/luban-excels/bak/xlsx/__enums__ - 副本.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="184">
   <si>
     <t>##var</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>狗狗的各种状态枚举</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>Bespoke</t>
@@ -2185,313 +2188,321 @@
       <c r="H33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="J33" s="1">
-        <v>2</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:11">
       <c r="H34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J34" s="1">
-        <v>1001</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="35" spans="2:11">
       <c r="H35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1001</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J35" s="1">
-        <v>1002</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="H36" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="J36" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="37" spans="2:11">
       <c r="H37" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="J37" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="38" spans="2:11">
       <c r="H38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="J38" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="39" spans="2:11">
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="H39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="J39" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="40" spans="2:11">
       <c r="H40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="J40" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="41" spans="2:11">
       <c r="H41" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="1">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="H42" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J41" s="1">
+      <c r="I42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J42" s="1">
         <v>1008</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="H42" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="J42" s="5">
-        <v>2001</v>
       </c>
     </row>
     <row r="43" spans="2:11">
       <c r="H43" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I43" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="J43" s="5">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="44" spans="2:11">
       <c r="H44" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="J44" s="5">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11">
+      <c r="H45" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="J44" s="5">
+      <c r="I45" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J45" s="5">
         <v>2003</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11">
-      <c r="H45" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J45" s="5">
-        <v>2004</v>
       </c>
     </row>
     <row r="46" spans="2:11">
       <c r="H46" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="J46" s="5">
-        <v>2005</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>130</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="47" spans="2:11">
       <c r="H47" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J47" s="5">
+        <v>2005</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I47" s="1" t="s">
+    </row>
+    <row r="48" spans="2:11">
+      <c r="H48" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J47" s="5">
+      <c r="I48" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J48" s="5">
         <v>2006</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="H48" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J48" s="5">
-        <v>2007</v>
       </c>
     </row>
     <row r="49" spans="8:10">
       <c r="H49" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="J49" s="5">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="50" spans="8:10">
+      <c r="H50" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="J49" s="5">
+      <c r="I50" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J50" s="5">
         <v>2008</v>
-      </c>
-    </row>
-    <row r="50" spans="8:10">
-      <c r="H50" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J50" s="1">
-        <v>3001</v>
       </c>
     </row>
     <row r="51" spans="8:10">
       <c r="H51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="J51" s="1">
-        <v>3002</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="52" spans="8:10">
       <c r="H52" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="J52" s="1">
-        <v>3003</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="53" spans="8:10">
       <c r="H53" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="J53" s="1">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="54" spans="8:10">
       <c r="H54" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="J54" s="1">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="55" spans="8:10">
       <c r="H55" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J55" s="1">
-        <v>3006</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="56" spans="8:10">
       <c r="H56" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J56" s="1">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="57" spans="8:10">
       <c r="H57" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="J57" s="1">
-        <v>3008</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="58" spans="8:10">
       <c r="H58" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="J58" s="1">
-        <v>3009</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="59" spans="8:10">
       <c r="H59" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="J59" s="1">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="60" spans="8:10">
+      <c r="H60" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J59" s="1">
+      <c r="I60" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J60" s="1">
         <v>3010</v>
       </c>
     </row>
     <row r="65" spans="2:10">
       <c r="B65" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C65" s="5" t="b">
         <v>0</v>
@@ -2500,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J65" s="1">
         <v>1</v>
@@ -2514,10 +2525,10 @@
     </row>
     <row r="66" spans="2:10">
       <c r="H66" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J66" s="1">
         <v>2</v>
@@ -2525,10 +2536,10 @@
     </row>
     <row r="67" spans="2:10">
       <c r="H67" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J67" s="1">
         <v>3</v>
@@ -2538,10 +2549,10 @@
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="H68" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J68" s="1">
         <v>4</v>
@@ -2549,10 +2560,10 @@
     </row>
     <row r="69" spans="2:10">
       <c r="H69" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J69" s="1">
         <v>5</v>
@@ -2560,10 +2571,10 @@
     </row>
     <row r="70" spans="2:10">
       <c r="H70" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J70" s="1">
         <v>6</v>
@@ -2571,10 +2582,10 @@
     </row>
     <row r="71" spans="2:10">
       <c r="H71" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J71" s="1">
         <v>7</v>
@@ -2582,10 +2593,10 @@
     </row>
     <row r="72" spans="2:10">
       <c r="H72" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J72" s="1">
         <v>8</v>
@@ -2595,10 +2606,10 @@
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="H73" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J73" s="1">
         <v>9</v>
@@ -2606,10 +2617,10 @@
     </row>
     <row r="74" spans="2:10">
       <c r="H74" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J74" s="1">
         <v>10</v>
@@ -2617,7 +2628,7 @@
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C98" s="5" t="b">
         <v>0</v>
@@ -2626,20 +2637,20 @@
         <v>1</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99" spans="2:9">
       <c r="H99" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="100" spans="2:9">
       <c r="H100" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="111" spans="2:9">
